--- a/세모이 자판 설명/세모이 자판 약어 (빈도순).xlsx
+++ b/세모이 자판 설명/세모이 자판 약어 (빈도순).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f585cdba73fdfdd1/바탕 화면/세모이 230116/dist/세모이 자판 설명/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="11_E6C820F64625210A87B2E6D3788AF465CDC4C73B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F68EB0BC-C3EE-4013-B7E8-FF57506455F5}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="11_E6C820F64625210A87B2E6D3788AF465CDC4C73B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8BB6D796-5AD7-48F5-AD00-3F2EA584B856}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="0" windowWidth="29010" windowHeight="15945" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28695" yWindow="15840" windowWidth="29010" windowHeight="15945" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -7411,7 +7411,7 @@
       <c r="L9" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="N9" s="2" t="s">
+      <c r="M9" s="2" t="s">
         <v>400</v>
       </c>
     </row>
@@ -10772,7 +10772,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="119" spans="1:15" ht="16.5">
+    <row r="119" spans="1:15">
       <c r="A119" s="3">
         <v>110</v>
       </c>
@@ -17390,7 +17390,7 @@
       <c r="D531" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="E531" s="2" t="s">
+      <c r="F531" s="2" t="s">
         <v>498</v>
       </c>
     </row>
@@ -19606,7 +19606,7 @@
       <c r="D673" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="E673" s="2" t="s">
+      <c r="F673" s="2" t="s">
         <v>498</v>
       </c>
     </row>
